--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY24"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113581742</v>
+        <v>116614073</v>
       </c>
       <c r="B2" t="n">
-        <v>57414</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,40 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>592875</v>
+        <v>592964</v>
       </c>
       <c r="R2" t="n">
-        <v>7037515</v>
+        <v>7037473</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -751,12 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -783,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113581344</v>
+        <v>118394900</v>
       </c>
       <c r="B3" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -799,35 +783,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>592923</v>
+        <v>592795</v>
       </c>
       <c r="R3" t="n">
-        <v>7037443</v>
+        <v>7037530</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -854,12 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -886,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113581584</v>
+        <v>116612582</v>
       </c>
       <c r="B4" t="n">
-        <v>78507</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -902,35 +880,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592893</v>
+        <v>592859</v>
       </c>
       <c r="R4" t="n">
-        <v>7037451</v>
+        <v>7037452</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -957,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -987,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113581474</v>
+        <v>116614402</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1015,40 +977,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592919</v>
+        <v>592999</v>
       </c>
       <c r="R5" t="n">
-        <v>7037442</v>
+        <v>7037457</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1075,12 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1095,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116614073</v>
+        <v>116615013</v>
       </c>
       <c r="B6" t="n">
-        <v>90731</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1123,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592964</v>
+        <v>592981</v>
       </c>
       <c r="R6" t="n">
-        <v>7037473</v>
+        <v>7037438</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1209,15 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>116613190</v>
+        <v>118394548</v>
       </c>
       <c r="B7" t="n">
-        <v>57278</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1225,39 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592953</v>
+        <v>592917</v>
       </c>
       <c r="R7" t="n">
-        <v>7037449</v>
+        <v>7037606</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1284,12 +1225,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1316,57 +1257,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>116615321</v>
+        <v>120458405</v>
       </c>
       <c r="B8" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592979</v>
+        <v>592740</v>
       </c>
       <c r="R8" t="n">
-        <v>7037487</v>
+        <v>7037669</v>
       </c>
       <c r="S8" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,12 +1322,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1422,57 +1354,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>116612574</v>
+        <v>120458700</v>
       </c>
       <c r="B9" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79866</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>1353</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Ach.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592859</v>
+        <v>592805</v>
       </c>
       <c r="R9" t="n">
-        <v>7037452</v>
+        <v>7037672</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,12 +1419,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1528,54 +1451,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116615124</v>
+        <v>116612590</v>
       </c>
       <c r="B10" t="n">
-        <v>97773</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592972</v>
+        <v>592859</v>
       </c>
       <c r="R10" t="n">
-        <v>7037443</v>
+        <v>7037452</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1634,50 +1548,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>116612582</v>
+        <v>118394511</v>
       </c>
       <c r="B11" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592859</v>
+        <v>592897</v>
       </c>
       <c r="R11" t="n">
-        <v>7037452</v>
+        <v>7037596</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1704,12 +1613,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,27 +1633,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>116612590</v>
+        <v>118394571</v>
       </c>
       <c r="B12" t="n">
-        <v>90413</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1772,14 +1676,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592859</v>
+        <v>592904</v>
       </c>
       <c r="R12" t="n">
-        <v>7037452</v>
+        <v>7037610</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1806,12 +1710,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1838,50 +1742,46 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>116615013</v>
+        <v>113581344</v>
       </c>
       <c r="B13" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592981</v>
+        <v>592923</v>
       </c>
       <c r="R13" t="n">
-        <v>7037438</v>
+        <v>7037443</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1908,12 +1808,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1940,50 +1840,46 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>116614402</v>
+        <v>113581584</v>
       </c>
       <c r="B14" t="n">
-        <v>90448</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592999</v>
+        <v>592893</v>
       </c>
       <c r="R14" t="n">
-        <v>7037457</v>
+        <v>7037451</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2010,12 +1906,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2023-12-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2023-12-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2030,76 +1936,57 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118395848</v>
+        <v>118394175</v>
       </c>
       <c r="B15" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Torsbäcken (Torsbäcken), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592800</v>
+        <v>592836</v>
       </c>
       <c r="R15" t="n">
-        <v>7037518</v>
+        <v>7037557</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2146,76 +2033,57 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118395409</v>
+        <v>118394991</v>
       </c>
       <c r="B16" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Torsbäcken (Torsbäcken), Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592818</v>
+        <v>592784</v>
       </c>
       <c r="R16" t="n">
-        <v>7037493</v>
+        <v>7037670</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2274,64 +2142,45 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118395536</v>
+        <v>118526405</v>
       </c>
       <c r="B17" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80460</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592846</v>
+        <v>592786</v>
       </c>
       <c r="R17" t="n">
-        <v>7037473</v>
+        <v>7037676</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2358,12 +2207,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2390,54 +2249,51 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>118395885</v>
+        <v>113581474</v>
       </c>
       <c r="B18" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>25</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Torsbäcken (Torsbäcken), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592811</v>
+        <v>592919</v>
       </c>
       <c r="R18" t="n">
-        <v>7037505</v>
+        <v>7037442</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2464,12 +2320,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,71 +2340,62 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>118394008</v>
+        <v>116613190</v>
       </c>
       <c r="B19" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592866</v>
+        <v>592953</v>
       </c>
       <c r="R19" t="n">
-        <v>7037408</v>
+        <v>7037449</v>
       </c>
       <c r="S19" t="n">
         <v>20</v>
@@ -2575,12 +2422,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2607,64 +2454,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>118394003</v>
+        <v>113581742</v>
       </c>
       <c r="B20" t="n">
-        <v>97855</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592865</v>
+        <v>592875</v>
       </c>
       <c r="R20" t="n">
-        <v>7037409</v>
+        <v>7037515</v>
       </c>
       <c r="S20" t="n">
         <v>20</v>
@@ -2691,12 +2525,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2711,62 +2545,61 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>118394175</v>
+        <v>116612574</v>
       </c>
       <c r="B21" t="n">
-        <v>79602</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6461</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Torsbäcken (Torsbäcken), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592836</v>
+        <v>592859</v>
       </c>
       <c r="R21" t="n">
-        <v>7037557</v>
+        <v>7037452</v>
       </c>
       <c r="S21" t="n">
         <v>20</v>
@@ -2793,12 +2626,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2825,15 +2658,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>118525890</v>
+        <v>116615124</v>
       </c>
       <c r="B22" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2860,29 +2688,19 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592922</v>
+        <v>592972</v>
       </c>
       <c r="R22" t="n">
-        <v>7037555</v>
+        <v>7037443</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2909,22 +2727,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2939,27 +2747,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>118525447</v>
+        <v>116615321</v>
       </c>
       <c r="B23" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2986,29 +2789,19 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592953</v>
+        <v>592979</v>
       </c>
       <c r="R23" t="n">
-        <v>7037526</v>
+        <v>7037487</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -3035,22 +2828,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3065,27 +2848,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118525940</v>
+        <v>118393899</v>
       </c>
       <c r="B24" t="n">
-        <v>97858</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3112,12 +2890,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
@@ -3127,14 +2900,14 @@
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Ådals-Liden (Ådals-Liden), Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592911</v>
+        <v>592898</v>
       </c>
       <c r="R24" t="n">
-        <v>7037529</v>
+        <v>7037363</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3161,22 +2934,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3191,15 +2954,1574 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>118393942</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>592906</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7037351</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
           <t>Sofia Gustafsson</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
+      <c r="AX25" t="inlineStr">
         <is>
           <t>Sofia Gustafsson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>118394002</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>592840</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7037410</v>
+      </c>
+      <c r="S26" t="n">
+        <v>20</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>118394003</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>592865</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7037409</v>
+      </c>
+      <c r="S27" t="n">
+        <v>20</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>118394008</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>592866</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7037408</v>
+      </c>
+      <c r="S28" t="n">
+        <v>20</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>118394830</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>592867</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7037601</v>
+      </c>
+      <c r="S29" t="n">
+        <v>20</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>118395329</v>
+      </c>
+      <c r="B30" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>592850</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7037405</v>
+      </c>
+      <c r="S30" t="n">
+        <v>20</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>118395409</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>592818</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7037493</v>
+      </c>
+      <c r="S31" t="n">
+        <v>20</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>118395536</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>592846</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7037473</v>
+      </c>
+      <c r="S32" t="n">
+        <v>20</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>118395848</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>592800</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7037518</v>
+      </c>
+      <c r="S33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>118395885</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>592811</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7037505</v>
+      </c>
+      <c r="S34" t="n">
+        <v>20</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>118525447</v>
+      </c>
+      <c r="B35" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>592953</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7037526</v>
+      </c>
+      <c r="S35" t="n">
+        <v>20</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>118525890</v>
+      </c>
+      <c r="B36" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>592922</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7037555</v>
+      </c>
+      <c r="S36" t="n">
+        <v>20</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>118525940</v>
+      </c>
+      <c r="B37" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>592911</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7037529</v>
+      </c>
+      <c r="S37" t="n">
+        <v>20</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>118527007</v>
+      </c>
+      <c r="B38" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>592933</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7037365</v>
+      </c>
+      <c r="S38" t="n">
+        <v>20</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116614073</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394900</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116612582</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116614402</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615013</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394548</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120458405</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120458700</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116612590</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394511</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394571</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1837,6 +1897,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113581344</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1945,6 +2010,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113581584</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2042,6 +2112,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394175</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2139,6 +2214,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394991</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2246,6 +2326,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118526405</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2349,6 +2434,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113581474</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2451,6 +2541,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116613190</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2554,6 +2649,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113581742</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2655,6 +2755,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116612574</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2756,6 +2861,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615124</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2857,6 +2967,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116615321</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2963,6 +3078,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118393899</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3074,6 +3194,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118393942</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3180,6 +3305,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394002</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3291,6 +3421,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394003</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3397,6 +3532,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394008</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3498,6 +3638,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118394830</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3604,6 +3749,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395329</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3715,6 +3865,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395409</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3826,6 +3981,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395536</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3937,6 +4097,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395848</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395885</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4159,6 +4329,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525447</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4280,6 +4455,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525890</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4401,6 +4581,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525940</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4522,8 +4707,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118527007</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ38"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>116612582</v>
+        <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>91909</v>
+        <v>92336</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -895,37 +895,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>592859</v>
+        <v>592947</v>
       </c>
       <c r="R4" t="n">
-        <v>7037452</v>
+        <v>7037596</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -949,12 +949,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -969,24 +969,28 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116612582</t>
+          <t>https://artportalen.se/Sighting/136189475</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>116614402</v>
+        <v>116612582</v>
       </c>
       <c r="B5" t="n">
         <v>91909</v>
@@ -1021,10 +1025,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>592999</v>
+        <v>592859</v>
       </c>
       <c r="R5" t="n">
-        <v>7037457</v>
+        <v>7037452</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1082,13 +1086,13 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116614402</t>
+          <t>https://artportalen.se/Sighting/116612582</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>116615013</v>
+        <v>116614402</v>
       </c>
       <c r="B6" t="n">
         <v>91909</v>
@@ -1123,10 +1127,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>592981</v>
+        <v>592999</v>
       </c>
       <c r="R6" t="n">
-        <v>7037438</v>
+        <v>7037457</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1184,13 +1188,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116615013</t>
+          <t>https://artportalen.se/Sighting/116614402</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>118394548</v>
+        <v>116615013</v>
       </c>
       <c r="B7" t="n">
         <v>91909</v>
@@ -1221,14 +1225,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>592917</v>
+        <v>592981</v>
       </c>
       <c r="R7" t="n">
-        <v>7037606</v>
+        <v>7037438</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1255,12 +1259,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1286,16 +1290,16 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394548</t>
+          <t>https://artportalen.se/Sighting/116615013</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120458405</v>
+        <v>118394548</v>
       </c>
       <c r="B8" t="n">
-        <v>92369</v>
+        <v>91909</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1303,21 +1307,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1209</v>
+        <v>1202</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,13 +1331,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>592740</v>
+        <v>592917</v>
       </c>
       <c r="R8" t="n">
-        <v>7037669</v>
+        <v>7037606</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1357,12 +1361,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1388,54 +1392,54 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120458405</t>
+          <t>https://artportalen.se/Sighting/118394548</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120458700</v>
+        <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>79866</v>
+        <v>92065</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1353</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Trådbrosklav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ramalina thrausta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Nyl.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>592805</v>
+        <v>592948</v>
       </c>
       <c r="R9" t="n">
-        <v>7037672</v>
+        <v>7037599</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1459,12 +1463,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-10-17</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1479,65 +1483,69 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/120458700</t>
+          <t>https://artportalen.se/Sighting/136189456</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>116612590</v>
+        <v>120458405</v>
       </c>
       <c r="B10" t="n">
-        <v>91872</v>
+        <v>92369</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>1209</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>592859</v>
+        <v>592740</v>
       </c>
       <c r="R10" t="n">
-        <v>7037452</v>
+        <v>7037669</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1561,12 +1569,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1592,54 +1600,54 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116612590</t>
+          <t>https://artportalen.se/Sighting/120458405</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>118394511</v>
+        <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>91872</v>
+        <v>83311</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>592897</v>
+        <v>592829</v>
       </c>
       <c r="R11" t="n">
-        <v>7037596</v>
+        <v>7037658</v>
       </c>
       <c r="S11" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1663,12 +1671,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1683,49 +1691,53 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394511</t>
+          <t>https://artportalen.se/Sighting/136189491</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>118394571</v>
+        <v>120458700</v>
       </c>
       <c r="B12" t="n">
-        <v>91872</v>
+        <v>79866</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5447</v>
+        <v>1353</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1735,13 +1747,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>592904</v>
+        <v>592805</v>
       </c>
       <c r="R12" t="n">
-        <v>7037610</v>
+        <v>7037672</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1765,12 +1777,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-10-17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1796,55 +1808,54 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394571</t>
+          <t>https://artportalen.se/Sighting/120458700</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113581344</v>
+        <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79327</v>
+        <v>79983</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>1353</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Trådbrosklav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramalina thrausta</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Nyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>592923</v>
+        <v>592812</v>
       </c>
       <c r="R13" t="n">
-        <v>7037443</v>
+        <v>7037662</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1868,12 +1879,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1888,63 +1899,66 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113581344</t>
+          <t>https://artportalen.se/Sighting/136189460</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113581584</v>
+        <v>116612590</v>
       </c>
       <c r="B14" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>592893</v>
+        <v>592859</v>
       </c>
       <c r="R14" t="n">
-        <v>7037451</v>
+        <v>7037452</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -1971,22 +1985,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>11:42</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2001,27 +2005,27 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113581584</t>
+          <t>https://artportalen.se/Sighting/116612590</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>118394175</v>
+        <v>118394511</v>
       </c>
       <c r="B15" t="n">
-        <v>80460</v>
+        <v>91872</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2029,21 +2033,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2053,10 +2057,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>592836</v>
+        <v>592897</v>
       </c>
       <c r="R15" t="n">
-        <v>7037557</v>
+        <v>7037596</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2103,27 +2107,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394175</t>
+          <t>https://artportalen.se/Sighting/118394511</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>118394991</v>
+        <v>118394571</v>
       </c>
       <c r="B16" t="n">
-        <v>80460</v>
+        <v>91872</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2131,21 +2135,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>5447</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2155,10 +2159,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>592784</v>
+        <v>592904</v>
       </c>
       <c r="R16" t="n">
-        <v>7037670</v>
+        <v>7037610</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2205,62 +2209,63 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394991</t>
+          <t>https://artportalen.se/Sighting/118394571</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>118526405</v>
+        <v>113581344</v>
       </c>
       <c r="B17" t="n">
-        <v>80460</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6461</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>592786</v>
+        <v>592923</v>
       </c>
       <c r="R17" t="n">
-        <v>7037676</v>
+        <v>7037443</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2287,22 +2292,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>12:19</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2317,68 +2312,63 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118526405</t>
+          <t>https://artportalen.se/Sighting/113581344</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113581474</v>
+        <v>113581584</v>
       </c>
       <c r="B18" t="n">
-        <v>57950</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
           <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>592919</v>
+        <v>592893</v>
       </c>
       <c r="R18" t="n">
-        <v>7037442</v>
+        <v>7037451</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2408,9 +2398,19 @@
           <t>2023-12-10</t>
         </is>
       </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>11:42</t>
+        </is>
+      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-12-10</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2436,59 +2436,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113581474</t>
+          <t>https://artportalen.se/Sighting/113581584</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>116613190</v>
+        <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>57953</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>592953</v>
+        <v>592825</v>
       </c>
       <c r="R19" t="n">
-        <v>7037449</v>
+        <v>7037654</v>
       </c>
       <c r="S19" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2512,12 +2507,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2532,71 +2527,69 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY19" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116613190</t>
+          <t>https://artportalen.se/Sighting/136189487</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>113581742</v>
+        <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>58114</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>592875</v>
+        <v>592816</v>
       </c>
       <c r="R20" t="n">
-        <v>7037515</v>
+        <v>7037654</v>
       </c>
       <c r="S20" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2620,12 +2613,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-12-10</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2640,69 +2633,69 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY20" t="inlineStr"/>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113581742</t>
+          <t>https://artportalen.se/Sighting/136189489</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>116612574</v>
+        <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>99118</v>
+        <v>83431</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6440</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>592859</v>
+        <v>592831</v>
       </c>
       <c r="R21" t="n">
-        <v>7037452</v>
+        <v>7037657</v>
       </c>
       <c r="S21" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2726,12 +2719,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2746,66 +2739,66 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Klara Elmquist</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116612574</t>
+          <t>https://artportalen.se/Sighting/136189451</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>116615124</v>
+        <v>118394175</v>
       </c>
       <c r="B22" t="n">
-        <v>99118</v>
+        <v>80460</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>592972</v>
+        <v>592836</v>
       </c>
       <c r="R22" t="n">
-        <v>7037443</v>
+        <v>7037557</v>
       </c>
       <c r="S22" t="n">
         <v>20</v>
@@ -2832,12 +2825,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2863,55 +2856,51 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116615124</t>
+          <t>https://artportalen.se/Sighting/118394175</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>116615321</v>
+        <v>118394991</v>
       </c>
       <c r="B23" t="n">
-        <v>99118</v>
+        <v>80460</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>592979</v>
+        <v>592784</v>
       </c>
       <c r="R23" t="n">
-        <v>7037487</v>
+        <v>7037670</v>
       </c>
       <c r="S23" t="n">
         <v>20</v>
@@ -2938,12 +2927,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2024-05-05</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2958,71 +2947,62 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/116615321</t>
+          <t>https://artportalen.se/Sighting/118394991</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>118393899</v>
+        <v>118526405</v>
       </c>
       <c r="B24" t="n">
-        <v>99118</v>
+        <v>80460</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220787</v>
+        <v>6461</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>592898</v>
+        <v>592786</v>
       </c>
       <c r="R24" t="n">
-        <v>7037363</v>
+        <v>7037676</v>
       </c>
       <c r="S24" t="n">
         <v>20</v>
@@ -3049,12 +3029,22 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3069,64 +3059,56 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118393899</t>
+          <t>https://artportalen.se/Sighting/118526405</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>118393942</v>
+        <v>113581474</v>
       </c>
       <c r="B25" t="n">
-        <v>99118</v>
+        <v>57950</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3135,10 +3117,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>592906</v>
+        <v>592919</v>
       </c>
       <c r="R25" t="n">
-        <v>7037351</v>
+        <v>7037442</v>
       </c>
       <c r="S25" t="n">
         <v>20</v>
@@ -3165,12 +3147,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3196,48 +3178,44 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118393942</t>
+          <t>https://artportalen.se/Sighting/113581474</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>118394002</v>
+        <v>116613190</v>
       </c>
       <c r="B26" t="n">
-        <v>99118</v>
+        <v>57953</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3246,10 +3224,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>592840</v>
+        <v>592953</v>
       </c>
       <c r="R26" t="n">
-        <v>7037410</v>
+        <v>7037449</v>
       </c>
       <c r="S26" t="n">
         <v>20</v>
@@ -3276,12 +3254,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3307,53 +3285,45 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394002</t>
+          <t>https://artportalen.se/Sighting/116613190</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>118394003</v>
+        <v>113581742</v>
       </c>
       <c r="B27" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
@@ -3362,10 +3332,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>592865</v>
+        <v>592875</v>
       </c>
       <c r="R27" t="n">
-        <v>7037409</v>
+        <v>7037515</v>
       </c>
       <c r="S27" t="n">
         <v>20</v>
@@ -3392,12 +3362,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2023-12-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3412,24 +3382,24 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394003</t>
+          <t>https://artportalen.se/Sighting/113581742</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>118394008</v>
+        <v>116612574</v>
       </c>
       <c r="B28" t="n">
         <v>99118</v>
@@ -3459,12 +3429,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
@@ -3473,10 +3438,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>592866</v>
+        <v>592859</v>
       </c>
       <c r="R28" t="n">
-        <v>7037408</v>
+        <v>7037452</v>
       </c>
       <c r="S28" t="n">
         <v>20</v>
@@ -3503,12 +3468,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3534,13 +3499,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394008</t>
+          <t>https://artportalen.se/Sighting/116612574</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>118394830</v>
+        <v>116615124</v>
       </c>
       <c r="B29" t="n">
         <v>99118</v>
@@ -3570,19 +3535,19 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>592867</v>
+        <v>592972</v>
       </c>
       <c r="R29" t="n">
-        <v>7037601</v>
+        <v>7037443</v>
       </c>
       <c r="S29" t="n">
         <v>20</v>
@@ -3609,12 +3574,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3640,13 +3605,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118394830</t>
+          <t>https://artportalen.se/Sighting/116615124</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>118395329</v>
+        <v>116615321</v>
       </c>
       <c r="B30" t="n">
         <v>99118</v>
@@ -3676,12 +3641,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3690,10 +3650,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>592850</v>
+        <v>592979</v>
       </c>
       <c r="R30" t="n">
-        <v>7037405</v>
+        <v>7037487</v>
       </c>
       <c r="S30" t="n">
         <v>20</v>
@@ -3720,12 +3680,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2024-07-12</t>
+          <t>2024-05-05</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3751,13 +3711,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118395329</t>
+          <t>https://artportalen.se/Sighting/116615321</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>118395409</v>
+        <v>118393899</v>
       </c>
       <c r="B31" t="n">
         <v>99118</v>
@@ -3790,26 +3750,21 @@
           <t>5</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>592818</v>
+        <v>592898</v>
       </c>
       <c r="R31" t="n">
-        <v>7037493</v>
+        <v>7037363</v>
       </c>
       <c r="S31" t="n">
         <v>20</v>
@@ -3856,24 +3811,24 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118395409</t>
+          <t>https://artportalen.se/Sighting/118393899</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>118395536</v>
+        <v>118393942</v>
       </c>
       <c r="B32" t="n">
         <v>99118</v>
@@ -3903,7 +3858,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3913,7 +3868,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>blomknopp</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -3922,10 +3877,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>592846</v>
+        <v>592906</v>
       </c>
       <c r="R32" t="n">
-        <v>7037473</v>
+        <v>7037351</v>
       </c>
       <c r="S32" t="n">
         <v>20</v>
@@ -3983,13 +3938,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118395536</t>
+          <t>https://artportalen.se/Sighting/118393942</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>118395848</v>
+        <v>118394002</v>
       </c>
       <c r="B33" t="n">
         <v>99118</v>
@@ -4019,12 +3974,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>10</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
@@ -4034,14 +3984,14 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>592800</v>
+        <v>592840</v>
       </c>
       <c r="R33" t="n">
-        <v>7037518</v>
+        <v>7037410</v>
       </c>
       <c r="S33" t="n">
         <v>20</v>
@@ -4088,24 +4038,24 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118395848</t>
+          <t>https://artportalen.se/Sighting/118394002</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>118395885</v>
+        <v>118394003</v>
       </c>
       <c r="B34" t="n">
         <v>99118</v>
@@ -4135,19 +4085,29 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Torsbäcken, Torsbäcken, Ång</t>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>592811</v>
+        <v>592865</v>
       </c>
       <c r="R34" t="n">
-        <v>7037505</v>
+        <v>7037409</v>
       </c>
       <c r="S34" t="n">
         <v>20</v>
@@ -4194,24 +4154,24 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Sofia Gustafsson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118395885</t>
+          <t>https://artportalen.se/Sighting/118394003</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>118525447</v>
+        <v>118394008</v>
       </c>
       <c r="B35" t="n">
         <v>99118</v>
@@ -4241,12 +4201,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
@@ -4260,10 +4215,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>592953</v>
+        <v>592866</v>
       </c>
       <c r="R35" t="n">
-        <v>7037526</v>
+        <v>7037408</v>
       </c>
       <c r="S35" t="n">
         <v>20</v>
@@ -4290,22 +4245,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>11:40</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4320,24 +4265,24 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118525447</t>
+          <t>https://artportalen.se/Sighting/118394008</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>118525890</v>
+        <v>118394830</v>
       </c>
       <c r="B36" t="n">
         <v>99118</v>
@@ -4367,29 +4312,19 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>592922</v>
+        <v>592867</v>
       </c>
       <c r="R36" t="n">
-        <v>7037555</v>
+        <v>7037601</v>
       </c>
       <c r="S36" t="n">
         <v>20</v>
@@ -4416,22 +4351,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>11:53</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4446,24 +4371,24 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118525890</t>
+          <t>https://artportalen.se/Sighting/118394830</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>118525940</v>
+        <v>118395329</v>
       </c>
       <c r="B37" t="n">
         <v>99118</v>
@@ -4493,12 +4418,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
@@ -4512,10 +4432,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>592911</v>
+        <v>592850</v>
       </c>
       <c r="R37" t="n">
-        <v>7037529</v>
+        <v>7037405</v>
       </c>
       <c r="S37" t="n">
         <v>20</v>
@@ -4542,22 +4462,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>11:56</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4572,24 +4482,24 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Sofia Gustafsson</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118525940</t>
+          <t>https://artportalen.se/Sighting/118395329</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>118527007</v>
+        <v>118395409</v>
       </c>
       <c r="B38" t="n">
         <v>99118</v>
@@ -4619,7 +4529,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -4629,19 +4539,19 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>blomknopp</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>592933</v>
+        <v>592818</v>
       </c>
       <c r="R38" t="n">
-        <v>7037365</v>
+        <v>7037493</v>
       </c>
       <c r="S38" t="n">
         <v>20</v>
@@ -4668,22 +4578,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="Z38" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2024-07-18</t>
-        </is>
-      </c>
-      <c r="AB38" t="inlineStr">
-        <is>
-          <t>12:45</t>
+          <t>2024-07-12</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4709,7 +4609,1061 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
+          <t>https://artportalen.se/Sighting/118395409</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>118395536</v>
+      </c>
+      <c r="B39" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>592846</v>
+      </c>
+      <c r="R39" t="n">
+        <v>7037473</v>
+      </c>
+      <c r="S39" t="n">
+        <v>20</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395536</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>118395848</v>
+      </c>
+      <c r="B40" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>592800</v>
+      </c>
+      <c r="R40" t="n">
+        <v>7037518</v>
+      </c>
+      <c r="S40" t="n">
+        <v>20</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395848</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>118395885</v>
+      </c>
+      <c r="B41" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>592811</v>
+      </c>
+      <c r="R41" t="n">
+        <v>7037505</v>
+      </c>
+      <c r="S41" t="n">
+        <v>20</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2024-07-12</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118395885</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>118525447</v>
+      </c>
+      <c r="B42" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>592953</v>
+      </c>
+      <c r="R42" t="n">
+        <v>7037526</v>
+      </c>
+      <c r="S42" t="n">
+        <v>20</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525447</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>118525890</v>
+      </c>
+      <c r="B43" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>592922</v>
+      </c>
+      <c r="R43" t="n">
+        <v>7037555</v>
+      </c>
+      <c r="S43" t="n">
+        <v>20</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525890</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>118525940</v>
+      </c>
+      <c r="B44" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>592911</v>
+      </c>
+      <c r="R44" t="n">
+        <v>7037529</v>
+      </c>
+      <c r="S44" t="n">
+        <v>20</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>11:56</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118525940</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>118527007</v>
+      </c>
+      <c r="B45" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Ådals-Liden, Ådals-Liden, Ång</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>592933</v>
+      </c>
+      <c r="R45" t="n">
+        <v>7037365</v>
+      </c>
+      <c r="S45" t="n">
+        <v>20</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2024-07-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>12:45</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Sofia Gustafsson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
           <t>https://artportalen.se/Sighting/118527007</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>136189484</v>
+      </c>
+      <c r="B46" t="n">
+        <v>99294</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>592813</v>
+      </c>
+      <c r="R46" t="n">
+        <v>7037670</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189484</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>136189493</v>
+      </c>
+      <c r="B47" t="n">
+        <v>104441</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>222395</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Dvärghäxört</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Circaea alpina</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Torsbäcken, Ång</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>592943</v>
+      </c>
+      <c r="R47" t="n">
+        <v>7037603</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Ådals-Liden</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Klara Elmquist</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Klara Elmquist, Maja Wressel</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr">
+        <is>
+          <t>Sweco naturvärdesinventering och artinventering</t>
+        </is>
+      </c>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136189493</t>
         </is>
       </c>
     </row>
@@ -4752,6 +5706,15 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92336</v>
+        <v>92337</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104441</v>
+        <v>104442</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92337</v>
+        <v>92338</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83311</v>
+        <v>83312</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79983</v>
+        <v>79984</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83431</v>
+        <v>83432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104442</v>
+        <v>104443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92338</v>
+        <v>92344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83312</v>
+        <v>83316</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79984</v>
+        <v>79988</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83432</v>
+        <v>83436</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104443</v>
+        <v>104449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92344</v>
+        <v>92345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83316</v>
+        <v>83317</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79988</v>
+        <v>79989</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83436</v>
+        <v>83437</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104449</v>
+        <v>104450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92345</v>
+        <v>92351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83317</v>
+        <v>83321</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79989</v>
+        <v>79993</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79450</v>
+        <v>79454</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83437</v>
+        <v>83441</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99303</v>
+        <v>99314</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104450</v>
+        <v>104461</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92351</v>
+        <v>92358</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83321</v>
+        <v>83327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79993</v>
+        <v>79999</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79454</v>
+        <v>79460</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83441</v>
+        <v>83447</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99314</v>
+        <v>99327</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104461</v>
+        <v>104474</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92358</v>
+        <v>92359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99327</v>
+        <v>99328</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104474</v>
+        <v>104475</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92359</v>
+        <v>92372</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83327</v>
+        <v>83340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>79999</v>
+        <v>80012</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79460</v>
+        <v>79473</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83447</v>
+        <v>83460</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99328</v>
+        <v>99341</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104475</v>
+        <v>104488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>

--- a/artfynd/A 57790-2024 artfynd.xlsx
+++ b/artfynd/A 57790-2024 artfynd.xlsx
@@ -887,7 +887,7 @@
         <v>136189475</v>
       </c>
       <c r="B4" t="n">
-        <v>92372</v>
+        <v>92373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1401,7 +1401,7 @@
         <v>136189456</v>
       </c>
       <c r="B9" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>136189491</v>
       </c>
       <c r="B11" t="n">
-        <v>83340</v>
+        <v>83341</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1817,7 +1817,7 @@
         <v>136189460</v>
       </c>
       <c r="B13" t="n">
-        <v>80012</v>
+        <v>80013</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>136189487</v>
       </c>
       <c r="B19" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2551,7 +2551,7 @@
         <v>136189489</v>
       </c>
       <c r="B20" t="n">
-        <v>79473</v>
+        <v>79474</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2657,7 +2657,7 @@
         <v>136189451</v>
       </c>
       <c r="B21" t="n">
-        <v>83460</v>
+        <v>83461</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>136189484</v>
       </c>
       <c r="B46" t="n">
-        <v>99341</v>
+        <v>99342</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5566,7 +5566,7 @@
         <v>136189493</v>
       </c>
       <c r="B47" t="n">
-        <v>104488</v>
+        <v>104489</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
